--- a/data/trans_orig/IP1011-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP1011-Estudios-trans_orig.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4535</t>
+          <t>4471</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4790</t>
+          <t>4394</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>607</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6558</t>
+          <t>5936</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>411552</t>
+          <t>411616</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>472201</t>
+          <t>472597</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>886520</t>
+          <t>887142</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>892414</t>
+          <t>892471</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3375</t>
+          <t>3988</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>2789</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>154763</t>
+          <t>154150</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>329175</t>
+          <t>329416</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>5134</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>601</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6387</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7740</t>
+          <t>6811</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>677099</t>
+          <t>675887</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>715587</t>
+          <t>716647</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>721371</t>
+          <t>721373</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1395255</t>
+          <t>1396184</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1401727</t>
+          <t>1401786</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3307</t>
+          <t>4384</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3059</t>
+          <t>3342</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>3987</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>88582</t>
+          <t>87505</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>80478</t>
+          <t>80195</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>170099</t>
+          <t>171438</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3797</t>
+          <t>3791</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3778</t>
+          <t>4268</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,45%</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>445903</t>
+          <t>445909</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>938325</t>
+          <t>937835</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4048</t>
+          <t>3185</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>5128</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -3169,7 +3169,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>167513</t>
+          <t>168376</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>333539</t>
+          <t>331773</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4963</t>
+          <t>4813</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4661</t>
+          <t>4588</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>670</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6253</t>
+          <t>6834</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>701965</t>
+          <t>702115</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>742840</t>
+          <t>742913</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1448176</t>
+          <t>1447595</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1453756</t>
+          <t>1453759</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3860</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3567</t>
+          <t>3547</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>183635</t>
+          <t>183570</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>356630</t>
+          <t>356650</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>2878</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4099</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>741281</t>
+          <t>741966</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5150,7 +5150,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1445116</t>
+          <t>1445301</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">

--- a/data/trans_orig/IP1011-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP1011-Estudios-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -835,47 +835,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>90867</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1070,94 +1070,94 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>1368</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4826</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>1266</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4471</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3907</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,3%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1368</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4394</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>2634</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>664</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>6625</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>2634</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>5936</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,07%</t>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -1178,102 +1178,102 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>475623</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>472165</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,71%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,99%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>626</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>414821</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>411616</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>412180</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,7%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,93%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>99,06%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>717</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>475623</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>472597</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1343</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>890444</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>886453</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>892414</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
         <is>
           <t>99,71%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>99,08%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1343</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>890444</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>887142</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>892471</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>99,71%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>628</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>719</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,107 +1408,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>602</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2677</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>602</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3988</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3366</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>602</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>2789</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -1521,72 +1521,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>157536</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>155461</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,62%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>98,31%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>157536</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>154150</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,62%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>329416</t>
+          <t>328839</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>603</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5826</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1266</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5134</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4386</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1970</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>601</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5327</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1209</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6811</t>
+          <t>7686</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1082</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>720004</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>716148</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>721371</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>99,19%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,92%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1016</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>679755</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>675887</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>676635</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,81%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>99,25%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>99,36%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1082</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>720004</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>716647</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>721373</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>99,26%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,92%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>2098</t>
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1396184</t>
+          <t>1395309</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1401786</t>
+          <t>1401725</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1085</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1085</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2157,7 +2157,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2330,102 +2330,102 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3403</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4,07%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>656</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4384</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3628</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,71%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,77%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>651</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>3,95%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1307</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3342</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4409</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>4,0%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1307</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3987</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -2438,74 +2438,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>82886</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>80134</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,22%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>95,93%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>91233</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>87505</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>88261</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>91889</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,29%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>95,23%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>96,05%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>82886</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>80195</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,22%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>96,0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>248</t>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>171438</t>
+          <t>171016</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2551,57 +2551,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2668,107 +2668,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>756</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3791</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5035</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,17%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>756</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4292</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>756</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4268</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -2781,74 +2781,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>650</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>448944</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>445909</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>444665</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>449700</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,83%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>99,16%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,88%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1355</t>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>937835</t>
+          <t>937811</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -2894,57 +2894,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>651</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>449700</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>449700</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>449700</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3011,107 +3011,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2742</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>672</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3185</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3381</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>672</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>5128</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -3124,72 +3124,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>170889</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>168819</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,61%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>98,4%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>165340</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>170889</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>168376</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,61%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>331773</t>
+          <t>333520</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3237,57 +3237,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3359,67 +3359,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>1323</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4639</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>1412</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4813</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4369</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1323</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4588</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>674</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6834</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>
@@ -3467,74 +3467,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1063</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>746178</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>742862</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>747501</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,82%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>99,38%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1016</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>705516</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>702115</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>702559</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,8%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>99,32%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>99,38%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1063</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>746178</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>742913</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>747501</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,82%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>99,39%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>2079</t>
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1447595</t>
+          <t>1448240</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1453759</t>
+          <t>1453755</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3580,57 +3580,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>747501</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>747501</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>747501</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>747501</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>747501</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>747501</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3760,7 +3760,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4041,47 +4041,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>59378</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4154,57 +4154,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4384,47 +4384,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>714</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>472290</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -4497,57 +4497,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>714</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4614,107 +4614,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3376</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>713</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3925</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3564</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3547</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -4727,72 +4727,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>186782</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>184119</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,62%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>98,2%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>186782</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>183570</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,62%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>356650</t>
+          <t>356633</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4840,57 +4840,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4957,107 +4957,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3938</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>713</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2878</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3553</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,05%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3914</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,05%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
     </row>
@@ -5070,72 +5070,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1064</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>744131</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>740906</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,9%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>99,47%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1064</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>744131</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>741966</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,9%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,7 +5150,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1445301</t>
+          <t>1445662</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5183,57 +5183,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
